--- a/data/trans_orig/IP16A09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58233</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79676</t>
+          <t>79239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24118</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51577</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58093</t>
+          <t>58364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>34713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>63848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116111</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123039</t>
+          <t>122929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136135</t>
+          <t>136723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142627</t>
+          <t>142631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254878</t>
+          <t>255652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264326</t>
+          <t>264403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>33573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74603</t>
+          <t>74863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46784</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>47687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96373</t>
+          <t>96290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102058</t>
+          <t>102056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>39188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88918</t>
+          <t>89125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94042</t>
+          <t>94038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>47247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44879</t>
+          <t>44288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>49303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93978</t>
+          <t>93893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99966</t>
+          <t>99978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178321</t>
+          <t>179419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185854</t>
+          <t>185759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180873</t>
+          <t>180978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188838</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>363259</t>
+          <t>363658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373367</t>
+          <t>373604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50015</t>
+          <t>50549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99795</t>
+          <t>100029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58407</t>
+          <t>58225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157406</t>
+          <t>156684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161969</t>
+          <t>161966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141737</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147422</t>
+          <t>147418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301701</t>
+          <t>300782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308416</t>
+          <t>308270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3468</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3041</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32220</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29817</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29350</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,43%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>89</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57858</t>
+          <t>58451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40600</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37902</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37869</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>127</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79239</t>
+          <t>79241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5175</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2760</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5681</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5877</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33186</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29948</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34487</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22404</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19483</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24121</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19287</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24159</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33186</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30346</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34489</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>51611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58364</t>
+          <t>57978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>793</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37482</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34782</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24884</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21727</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21833</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,03%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37482</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34713</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>58728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63848</t>
+          <t>63840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7416</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9976</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7196</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136503</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142637</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>120108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>115866</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122929</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>115329</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>122777</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140647</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136723</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>142631</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255652</t>
+          <t>255911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264403</t>
+          <t>264678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1637</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5773</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5525</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34120</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37709</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33573</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74863</t>
+          <t>73940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2900,52 +2900,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5707</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3276</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50316</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47574</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>50148</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46030</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>46876</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,61%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50316</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47687</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>147</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96290</t>
+          <t>96029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102056</t>
+          <t>102055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,67 +3360,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4422</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1126</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3832</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49993</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46806</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>42303</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39188</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39439</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>49993</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47396</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89125</t>
+          <t>89193</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94038</t>
+          <t>94044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5524</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3537</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3560</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5653</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47878</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44417</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49296</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>49997</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47247</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>47224</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47878</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>44288</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49303</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,87%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>131</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93893</t>
+          <t>94191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99978</t>
+          <t>100015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10721</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7573</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2493</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>185896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>180757</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>188867</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>183491</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179419</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>185759</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>179223</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>185725</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>185896</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>180978</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>188985</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>363658</t>
+          <t>363026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373604</t>
+          <t>373364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>560</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31504</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28515</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29667</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>80</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>57886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2869</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3351</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3150</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52854</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50549</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50558</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>159</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100029</t>
+          <t>99828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1153</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6316</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29575</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25706</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31660</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>32795</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29951</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29940</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,19%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29575</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26058</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31661</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>80,49%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>102</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>64909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>43106</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,67 +5993,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2277</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5852</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145326</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>141204</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147420</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>160259</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>156684</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161966</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>156588</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>161965</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>145326</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>141108</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147418</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>452</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300782</t>
+          <t>300894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308270</t>
+          <t>308356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
